--- a/branches/main/StructureDefinition-mii-pr-icu-score-numerische-ratingskala.xlsx
+++ b/branches/main/StructureDefinition-mii-pr-icu-score-numerische-ratingskala.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T11:25:36+00:00</t>
+    <t>2026-10-21T14:50:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
